--- a/excel/Ch10_Depreciation.xlsx
+++ b/excel/Ch10_Depreciation.xlsx
@@ -243,7 +243,7 @@
     <t xml:space="preserve">Useful life (years)</t>
   </si>
   <si>
-    <t xml:space="preserve">Q2 (Model Question 10.9): Musa's machine, reducing balance</t>
+    <t xml:space="preserve">Q2 (Model Question 10.12): Musa's machine, reducing balance</t>
   </si>
   <si>
     <t xml:space="preserve">Cost on 1 January 2023</t>
@@ -267,7 +267,7 @@
     <t xml:space="preserve">Value at end of year</t>
   </si>
   <si>
-    <t xml:space="preserve">Q4 (Model Question 10.10): part year</t>
+    <t xml:space="preserve">Q4 (Model Question 10.11): part year</t>
   </si>
   <si>
     <t xml:space="preserve">Rate on cost per year</t>
